--- a/metadata/sdot-schema-mapping.xlsx
+++ b/metadata/sdot-schema-mapping.xlsx
@@ -2,102 +2,48 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4180" yWindow="600" windowWidth="29420" windowHeight="20400" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FileInventory" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ColumnMapping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="2">
     <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.8999908444471572"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -108,40 +54,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -214,7 +138,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -224,44 +148,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -288,32 +212,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -340,24 +246,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -369,162 +257,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -538,82 +430,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>file_order</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>relative_path</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>file_size_mb</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>encoding</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>row_count</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>col_count</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>all_columns_list</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>column_hash</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>schema_version</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>target_time_col</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>period_type</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>start_date</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
@@ -628,7 +520,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.04.01-04.30.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.04.01-04.30.csv</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -700,7 +592,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.05.01-05.31.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.05.01-05.31.csv</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,7 +664,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.06.01-06.30.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.06.01-06.30.csv</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -844,7 +736,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.07.01-07.31.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.07.01-07.31.csv</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -916,7 +808,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.08.01-08.31.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.08.01-08.31.csv</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -988,7 +880,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.09.01-09.30.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.09.01-09.30.csv</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1060,7 +952,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.10.01-10.31.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.10.01-10.31.csv</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1132,7 +1024,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.11.01-11.08.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.11.01-11.08.csv</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1204,7 +1096,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.11.09-11.15.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.11.09-11.15.csv</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1276,7 +1168,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.11.16-11.22.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.11.16-11.22.csv</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1348,7 +1240,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.11.23-11.29.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.11.23-11.29.csv</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1420,7 +1312,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.11.30-12.06.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.11.30-12.06.csv</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1492,7 +1384,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.12.07-12.13.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.12.07-12.13.csv</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1564,7 +1456,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.12.14-12.20.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.12.14-12.20.csv</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1636,7 +1528,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.12.21-12.27.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.12.21-12.27.csv</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1708,7 +1600,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>S-DoT_2020/S-DoT_NATURE_2020.12.28-01.03.csv</t>
+          <t>S-DoT/S-DoT_2020/S-DoT_NATURE_2020.12.28-01.03.csv</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1780,7 +1672,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.01.04-01.10.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.01.04-01.10.csv</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1852,7 +1744,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.01.11-01.17.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.01.11-01.17.csv</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1924,7 +1816,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.01.18-01.24.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.01.18-01.24.csv</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1996,7 +1888,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.01.25-01.31.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.01.25-01.31.csv</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2068,7 +1960,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.02.01-02.07.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.02.01-02.07.csv</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2140,7 +2032,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.02.08-02.14.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.02.08-02.14.csv</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,7 +2104,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.02.15-02.21.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.02.15-02.21.csv</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2284,7 +2176,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.02.22-02.28.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.02.22-02.28.csv</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2356,7 +2248,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.03.01-03.07.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.03.01-03.07.csv</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2428,7 +2320,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.03.08-03.14.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.03.08-03.14.csv</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2500,7 +2392,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.03.15-03.21.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.03.15-03.21.csv</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2572,7 +2464,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.03.22-03.28.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.03.22-03.28.csv</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2644,7 +2536,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.03.29-04.04.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.03.29-04.04.csv</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2716,7 +2608,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.04.05-04.11.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.04.05-04.11.csv</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2788,7 +2680,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.04.12-04.18.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.04.12-04.18.csv</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2860,7 +2752,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.04.19-04.25.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.04.19-04.25.csv</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2932,7 +2824,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.04.26-05.02.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.04.26-05.02.csv</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3004,7 +2896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.05.03-05.09.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.05.03-05.09.csv</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3076,7 +2968,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.05.10-05.16.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.05.10-05.16.csv</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3148,7 +3040,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.05.17-05.23.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.05.17-05.23.csv</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3220,7 +3112,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.05.24-05.30.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.05.24-05.30.csv</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3292,7 +3184,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.05.31-06.06.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.05.31-06.06.csv</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3364,7 +3256,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.06.07-06.13.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.06.07-06.13.csv</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3436,7 +3328,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.06.14-06.20.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.06.14-06.20.csv</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3508,7 +3400,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.06.21-06.27.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.06.21-06.27.csv</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3580,7 +3472,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.06.28-07.04.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.06.28-07.04.csv</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3652,7 +3544,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.07.05-07.11.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.07.05-07.11.csv</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3724,7 +3616,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.07.12-07.18.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.07.12-07.18.csv</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3796,7 +3688,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.07.19-07.25.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.07.19-07.25.csv</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3868,7 +3760,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.07.26-08.01.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.07.26-08.01.csv</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3940,7 +3832,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.08.02-08.08.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.08.02-08.08.csv</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4012,7 +3904,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.08.09-08.15.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.08.09-08.15.csv</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4084,7 +3976,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.08.16-08.22.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.08.16-08.22.csv</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4156,7 +4048,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.08.23-08.29.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.08.23-08.29.csv</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4228,7 +4120,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.08.30-09.05.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.08.30-09.05.csv</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4300,7 +4192,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.09.06-09.12.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.09.06-09.12.csv</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4372,7 +4264,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.09.13-09.19.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.09.13-09.19.csv</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4444,7 +4336,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.09.20-09.26.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.09.20-09.26.csv</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4516,7 +4408,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.09.27-10.03.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.09.27-10.03.csv</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4588,7 +4480,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.09.30-10.05.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.09.30-10.05.csv</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4660,7 +4552,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.10.04-10.10.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.10.04-10.10.csv</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4732,7 +4624,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.10.11-10.17.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.10.11-10.17.csv</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4804,7 +4696,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.10.18-10.24.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.10.18-10.24.csv</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4876,7 +4768,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.10.25-10.31.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.10.25-10.31.csv</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4948,7 +4840,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.11.01-11.07.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.11.01-11.07.csv</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5020,7 +4912,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.11.08.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.11.08.csv</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5092,7 +4984,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.11.09-11.14.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.11.09-11.14.csv</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5164,7 +5056,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.11.15-11.21.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.11.15-11.21.csv</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5236,7 +5128,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.11.16-11.22.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.11.16-11.22.csv</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5308,7 +5200,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.11.22-11.28.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.11.22-11.28.csv</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5380,7 +5272,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.11.29-12.05.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.11.29-12.05.csv</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5452,7 +5344,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.12.06-12.12.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.12.06-12.12.csv</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5524,7 +5416,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.12.13-12.19.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.12.13-12.19.csv</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5596,7 +5488,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.12.20-12.26.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.12.20-12.26.csv</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5668,7 +5560,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>S-DoT_2021/S-DoT_NATURE_2021.12.27-01.02.csv</t>
+          <t>S-DoT/S-DoT_2021/S-DoT_NATURE_2021.12.27-01.02.csv</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5740,7 +5632,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.01.03-01.09.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.01.03-01.09.csv</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5812,7 +5704,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.01.10-01.16.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.01.10-01.16.csv</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5884,7 +5776,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.01.17-01.23.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.01.17-01.23.csv</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5956,7 +5848,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.01.24-01.30.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.01.24-01.30.csv</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6028,7 +5920,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.01.31-02.06.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.01.31-02.06.csv</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6100,7 +5992,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.02.07-02.13.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.02.07-02.13.csv</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6172,7 +6064,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.02.14-02.20.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.02.14-02.20.csv</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6244,7 +6136,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.02.21-02.27.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.02.21-02.27.csv</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6316,7 +6208,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.02.28-03.06.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.02.28-03.06.csv</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6388,7 +6280,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.03.07-03.13.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.03.07-03.13.csv</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6460,7 +6352,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.03.14-03.20.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.03.14-03.20.csv</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6532,7 +6424,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.03.21-03.27.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.03.21-03.27.csv</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6604,7 +6496,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.03.28-04.03.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.03.28-04.03.csv</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6676,7 +6568,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.04.04-04.10.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.04.04-04.10.csv</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6748,7 +6640,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.04.11-04.17.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.04.11-04.17.csv</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6820,7 +6712,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.04.18-04.24.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.04.18-04.24.csv</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6892,7 +6784,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.04.25-05.01.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.04.25-05.01.csv</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6964,7 +6856,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.05.02-05.08.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.05.02-05.08.csv</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7036,7 +6928,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.05.09-05.15.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.05.09-05.15.csv</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7108,7 +7000,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.05.16-05.22.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.05.16-05.22.csv</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7180,7 +7072,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.05.23-05.29.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.05.23-05.29.csv</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7252,7 +7144,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.05.30-06.05.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.05.30-06.05.csv</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7324,7 +7216,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.06.06-06.12.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.06.06-06.12.csv</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7396,7 +7288,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.06.13-06.19.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.06.13-06.19.csv</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -7468,7 +7360,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.06.20-06.26.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.06.20-06.26.csv</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -7540,7 +7432,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.06.27-07.03.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.06.27-07.03.csv</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -7612,7 +7504,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.07.04-07.10.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.07.04-07.10.csv</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -7684,7 +7576,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.07.11-07.17.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.07.11-07.17.csv</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -7756,7 +7648,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.07.18-07.24.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.07.18-07.24.csv</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -7828,7 +7720,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.07.25-07.31.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.07.25-07.31.csv</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -7900,7 +7792,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.08.01-08.07.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.08.01-08.07.csv</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7972,7 +7864,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.08.08-08.14.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.08.08-08.14.csv</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8044,7 +7936,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.08.15-08.21.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.08.15-08.21.csv</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8116,7 +8008,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.08.22-08.28.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.08.22-08.28.csv</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -8188,7 +8080,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.08.29-09.04.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.08.29-09.04.csv</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -8260,7 +8152,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.09.05-09.11.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.09.05-09.11.csv</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -8332,7 +8224,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.09.12-09.18.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.09.12-09.18.csv</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -8404,7 +8296,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.09.19-09.25.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.09.19-09.25.csv</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -8476,7 +8368,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.09.26-10.02.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.09.26-10.02.csv</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -8548,7 +8440,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.10.03-10.09.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.10.03-10.09.csv</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -8620,7 +8512,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.10.10-10.16.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.10.10-10.16.csv</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -8692,7 +8584,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.10.17-10.23.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.10.17-10.23.csv</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -8764,7 +8656,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.10.24-10.30.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.10.24-10.30.csv</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -8836,7 +8728,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.10.31-11.06.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.10.31-11.06.csv</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -8908,7 +8800,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.11.07-11.13.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.11.07-11.13.csv</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -8980,7 +8872,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.11.14-11.20.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.11.14-11.20.csv</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -9052,7 +8944,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.11.21-11.27.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.11.21-11.27.csv</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -9124,7 +9016,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.11.28-12.04.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.11.28-12.04.csv</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9196,7 +9088,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.12.05-12.11.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.12.05-12.11.csv</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -9268,7 +9160,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.12.12-12.13.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.12.12-12.13.csv</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -9340,7 +9232,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.12.14-12.18.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.12.14-12.18.csv</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -9412,7 +9304,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.12.19-12.25.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.12.19-12.25.csv</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -9484,7 +9376,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.12.26-12.28.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.12.26-12.28.csv</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -9556,7 +9448,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>S-DoT_2022/S-DoT_NATURE_2022.12.29-01.01.csv</t>
+          <t>S-DoT/S-DoT_2022/S-DoT_NATURE_2022.12.29-01.01.csv</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -9628,7 +9520,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.01.01.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.01.01.csv</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -9700,7 +9592,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.01.02-01.08.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.01.02-01.08.csv</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9772,7 +9664,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.01.09-01.15.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.01.09-01.15.csv</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -9844,7 +9736,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.01.16-01.22.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.01.16-01.22.csv</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -9916,7 +9808,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.01.23-01.29.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.01.23-01.29.csv</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -9988,7 +9880,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.01.30-02.05.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.01.30-02.05.csv</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -10060,7 +9952,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.02.06-02.12.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.02.06-02.12.csv</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -10132,7 +10024,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.02.13-02.19.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.02.13-02.19.csv</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -10204,7 +10096,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.02.20-02.26.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.02.20-02.26.csv</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -10276,7 +10168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.02.27-03.05.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.02.27-03.05.csv</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -10348,7 +10240,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.03.06-03.12.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.03.06-03.12.csv</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -10420,7 +10312,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.03.13-03.19.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.03.13-03.19.csv</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -10492,7 +10384,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.03.20-03.26.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.03.20-03.26.csv</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10564,7 +10456,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.03.27-04.02.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.03.27-04.02.csv</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -10636,7 +10528,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.04.03-04.09.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.04.03-04.09.csv</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -10708,7 +10600,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.04.10-04.16.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.04.10-04.16.csv</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -10780,7 +10672,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.04.17-04.23.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.04.17-04.23.csv</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -10852,7 +10744,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.04.24-04.30.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.04.24-04.30.csv</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -10924,7 +10816,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.05.01-05.07.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.05.01-05.07.csv</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -10996,7 +10888,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.05.08-05.14.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.05.08-05.14.csv</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -11068,7 +10960,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.05.15-05.21.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.05.15-05.21.csv</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -11140,7 +11032,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.05.22-05.28.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.05.22-05.28.csv</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -11212,7 +11104,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.05.29-06.04.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.05.29-06.04.csv</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -11284,7 +11176,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.06.05-06.11.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.06.05-06.11.csv</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -11356,7 +11248,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.06.12-06.18.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.06.12-06.18.csv</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -11428,7 +11320,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.06.19-06.25.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.06.19-06.25.csv</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -11500,7 +11392,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.06.26-07.02.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.06.26-07.02.csv</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -11572,7 +11464,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.07.03-07.09.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.07.03-07.09.csv</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -11644,7 +11536,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.07.10-07.16.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.07.10-07.16.csv</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -11716,7 +11608,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.07.17-07.23.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.07.17-07.23.csv</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -11788,7 +11680,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.07.24-07.30.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.07.24-07.30.csv</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -11860,7 +11752,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.07.31-08.06.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.07.31-08.06.csv</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -11932,7 +11824,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.08.07-08.13.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.08.07-08.13.csv</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -12004,7 +11896,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.08.14-08.20.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.08.14-08.20.csv</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -12076,7 +11968,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.08.21-08.27.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.08.21-08.27.csv</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -12148,7 +12040,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.08.28-09.03.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.08.28-09.03.csv</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -12220,7 +12112,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.09.04-09.10.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.09.04-09.10.csv</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -12292,7 +12184,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.09.11-09.17.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.09.11-09.17.csv</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -12364,7 +12256,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.09.18-09.24.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.09.18-09.24.csv</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -12436,7 +12328,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.09.25-10.01.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.09.25-10.01.csv</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -12508,7 +12400,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.10.02-10.08.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.10.02-10.08.csv</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -12580,7 +12472,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.10.09-10.15.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.10.09-10.15.csv</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -12652,7 +12544,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.10.16-10.22.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.10.16-10.22.csv</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -12724,7 +12616,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.10.23-10.29.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.10.23-10.29.csv</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -12796,7 +12688,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.10.30-11.05.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.10.30-11.05.csv</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -12868,7 +12760,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.11.06-11.12.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.11.06-11.12.csv</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -12940,7 +12832,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.11.13-11.19.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.11.13-11.19.csv</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -13012,7 +12904,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.11.20-11.26.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.11.20-11.26.csv</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -13084,7 +12976,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.11.27-12.03.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.11.27-12.03.csv</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -13156,7 +13048,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.12.04-12.10.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.12.04-12.10.csv</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -13228,7 +13120,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.12.11-12.17.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.12.11-12.17.csv</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -13300,7 +13192,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.12.18-12.24.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.12.18-12.24.csv</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -13372,7 +13264,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>S-DoT_2023/S-DoT_NATURE_2023.12.25-12.31.csv</t>
+          <t>S-DoT/S-DoT_2023/S-DoT_NATURE_2023.12.25-12.31.csv</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -13444,7 +13336,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202401.csv</t>
+          <t>S-DoT/S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202401.csv</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -13516,7 +13408,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202402.csv</t>
+          <t>S-DoT/S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202402.csv</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -13588,7 +13480,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202403.csv</t>
+          <t>S-DoT/S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202403.csv</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -13660,7 +13552,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202404.csv</t>
+          <t>S-DoT/S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202404.csv</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -13732,7 +13624,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202405.csv</t>
+          <t>S-DoT/S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202405.csv</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -13804,7 +13696,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202406.csv</t>
+          <t>S-DoT/S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202406.csv</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -13876,7 +13768,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202407.csv</t>
+          <t>S-DoT/S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202407.csv</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -13948,7 +13840,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202408.csv</t>
+          <t>S-DoT/S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202408.csv</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -14020,7 +13912,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202409.csv</t>
+          <t>S-DoT/S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202409.csv</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -14092,7 +13984,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202410.csv</t>
+          <t>S-DoT/S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202410.csv</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -14164,7 +14056,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202411.csv</t>
+          <t>S-DoT/S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202411.csv</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -14236,7 +14128,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202412.csv</t>
+          <t>S-DoT/S-DoT_2024/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_202412.csv</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -14308,7 +14200,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250101.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250101.csv</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -14380,7 +14272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250102.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250102.csv</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -14452,7 +14344,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250103.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250103.csv</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -14524,7 +14416,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250104.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250104.csv</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -14596,7 +14488,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250105.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250105.csv</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -14668,7 +14560,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250106.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250106.csv</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -14740,7 +14632,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250107.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250107.csv</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -14812,7 +14704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250108.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250108.csv</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -14884,7 +14776,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250109.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250109.csv</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -14956,7 +14848,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250110.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250110.csv</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -15028,7 +14920,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250111.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250111.csv</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -15100,7 +14992,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250112.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250112.csv</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -15172,7 +15064,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250113.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250113.csv</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -15244,7 +15136,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250114.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250114.csv</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -15316,7 +15208,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250115.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250115.csv</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -15388,7 +15280,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250116.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250116.csv</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -15460,7 +15352,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250117.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250117.csv</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -15532,7 +15424,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250118.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250118.csv</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -15604,7 +15496,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250119.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250119.csv</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -15676,7 +15568,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250120.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250120.csv</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -15748,7 +15640,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250121.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250121.csv</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -15820,7 +15712,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250122.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250122.csv</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -15892,7 +15784,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250123.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250123.csv</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -15964,7 +15856,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250124.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250124.csv</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -16036,7 +15928,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250125.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250125.csv</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -16108,7 +16000,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250126.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250126.csv</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -16180,7 +16072,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250127.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250127.csv</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -16252,7 +16144,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250128.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250128.csv</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -16324,7 +16216,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250129.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250129.csv</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -16396,7 +16288,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250130.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250130.csv</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -16468,7 +16360,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250131.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.01/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250131.csv</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -16540,7 +16432,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250201.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250201.csv</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -16612,7 +16504,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250202.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250202.csv</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -16684,7 +16576,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250203.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250203.csv</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -16756,7 +16648,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250204.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250204.csv</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -16828,7 +16720,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250205.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250205.csv</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -16900,7 +16792,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250206.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250206.csv</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -16972,7 +16864,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250207.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250207.csv</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -17044,7 +16936,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250208.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250208.csv</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -17116,7 +17008,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250209.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250209.csv</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -17188,7 +17080,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250210.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250210.csv</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -17260,7 +17152,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250211.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250211.csv</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -17332,7 +17224,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250212.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250212.csv</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -17404,7 +17296,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250213.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250213.csv</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -17476,7 +17368,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250214.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250214.csv</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -17548,7 +17440,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250215.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250215.csv</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -17620,7 +17512,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250216.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250216.csv</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -17692,7 +17584,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250217.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250217.csv</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -17764,7 +17656,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250218.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250218.csv</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -17836,7 +17728,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250219.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250219.csv</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -17908,7 +17800,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250220.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250220.csv</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -17980,7 +17872,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250221.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250221.csv</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -18052,7 +17944,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250222.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250222.csv</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -18124,7 +18016,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250223.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250223.csv</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -18196,7 +18088,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250224.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250224.csv</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -18268,7 +18160,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250225.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250225.csv</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -18340,7 +18232,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250226.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250226.csv</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -18412,7 +18304,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250227.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250227.csv</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -18484,7 +18376,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250228.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.02/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250228.csv</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -18556,7 +18448,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250301.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250301.csv</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -18628,7 +18520,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250302.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250302.csv</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -18700,7 +18592,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250303.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250303.csv</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -18772,7 +18664,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250304.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250304.csv</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -18844,7 +18736,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250305.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250305.csv</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -18916,7 +18808,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250306.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250306.csv</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -18988,7 +18880,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250307.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250307.csv</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -19060,7 +18952,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250308.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250308.csv</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -19132,7 +19024,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250309.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250309.csv</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -19204,7 +19096,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250310.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250310.csv</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -19276,7 +19168,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250311.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250311.csv</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -19348,7 +19240,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250312.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250312.csv</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -19420,7 +19312,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250313.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250313.csv</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -19492,7 +19384,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250314.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250314.csv</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -19564,7 +19456,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250315.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250315.csv</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -19636,7 +19528,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250316.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250316.csv</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -19708,7 +19600,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250317.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250317.csv</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -19780,7 +19672,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250318.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250318.csv</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -19852,7 +19744,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250319.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250319.csv</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -19924,7 +19816,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250320.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250320.csv</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -19996,7 +19888,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250321.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250321.csv</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -20068,7 +19960,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250322.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250322.csv</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -20140,7 +20032,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250323.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250323.csv</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -20212,7 +20104,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250324.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250324.csv</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -20284,7 +20176,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250325.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250325.csv</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -20356,7 +20248,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250326.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250326.csv</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -20428,7 +20320,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250327.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250327.csv</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -20500,7 +20392,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250328.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250328.csv</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -20572,7 +20464,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250329.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250329.csv</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -20644,7 +20536,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250330.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250330.csv</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -20716,7 +20608,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250331.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.03/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250331.csv</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -20788,7 +20680,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250401.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250401.csv</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -20860,7 +20752,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250402.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250402.csv</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -20932,7 +20824,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250403.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250403.csv</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -21004,7 +20896,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250404.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250404.csv</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -21076,7 +20968,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250405.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250405.csv</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -21148,7 +21040,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250406.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250406.csv</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -21220,7 +21112,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250407.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250407.csv</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -21292,7 +21184,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250408.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250408.csv</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -21364,7 +21256,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250409.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250409.csv</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -21436,7 +21328,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250410.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250410.csv</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -21508,7 +21400,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250411.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250411.csv</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -21580,7 +21472,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250412.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250412.csv</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -21652,7 +21544,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250413.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250413.csv</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -21724,7 +21616,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250414.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250414.csv</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -21796,7 +21688,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250415.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250415.csv</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -21868,7 +21760,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250416.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250416.csv</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -21940,7 +21832,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250417.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250417.csv</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -22012,7 +21904,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250418.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250418.csv</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -22084,7 +21976,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250419.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250419.csv</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -22156,7 +22048,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250420.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250420.csv</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -22228,7 +22120,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250421.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250421.csv</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -22300,7 +22192,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250422.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250422.csv</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -22372,7 +22264,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250423.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250423.csv</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -22444,7 +22336,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250424.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250424.csv</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -22516,7 +22408,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250425.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250425.csv</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -22588,7 +22480,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250426.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250426.csv</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -22660,7 +22552,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250427.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250427.csv</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -22732,7 +22624,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250428.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250428.csv</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -22804,7 +22696,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250429.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250429.csv</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -22876,7 +22768,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250430.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.04/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250430.csv</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -22948,7 +22840,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250501.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250501.csv</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -23020,7 +22912,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250502.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250502.csv</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -23092,7 +22984,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250503.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250503.csv</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -23164,7 +23056,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250504.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250504.csv</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -23236,7 +23128,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250505.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250505.csv</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -23308,7 +23200,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250506.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250506.csv</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -23380,7 +23272,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250507.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250507.csv</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -23452,7 +23344,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250508.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250508.csv</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -23524,7 +23416,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250509.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250509.csv</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -23596,7 +23488,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250510.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250510.csv</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -23668,7 +23560,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250511.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250511.csv</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -23740,7 +23632,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250512.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250512.csv</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -23812,7 +23704,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250513.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250513.csv</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -23884,7 +23776,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250514.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250514.csv</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -23956,7 +23848,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250515.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250515.csv</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -24028,7 +23920,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250516.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250516.csv</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -24100,7 +23992,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250517.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250517.csv</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -24172,7 +24064,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250518.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250518.csv</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -24244,7 +24136,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250519.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250519.csv</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -24316,7 +24208,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250520.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250520.csv</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -24388,7 +24280,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250521.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250521.csv</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -24460,7 +24352,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250522.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250522.csv</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -24532,7 +24424,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250523.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250523.csv</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -24604,7 +24496,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250524.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250524.csv</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -24676,7 +24568,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250525.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250525.csv</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -24748,7 +24640,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250526.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250526.csv</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -24820,7 +24712,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250527.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250527.csv</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -24892,7 +24784,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250528.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250528.csv</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -24964,7 +24856,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250529.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250529.csv</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -25036,7 +24928,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250530.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250530.csv</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -25108,7 +25000,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250531.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.05/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250531.csv</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -25180,7 +25072,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250601.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250601.csv</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -25252,7 +25144,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250602.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250602.csv</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -25324,7 +25216,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250603.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250603.csv</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -25396,7 +25288,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250604.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250604.csv</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -25468,7 +25360,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250605.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250605.csv</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -25540,7 +25432,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250606.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250606.csv</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -25612,7 +25504,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250607.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250607.csv</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -25684,7 +25576,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250608.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250608.csv</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -25756,7 +25648,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250609.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250609.csv</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -25828,7 +25720,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250610.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250610.csv</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -25900,7 +25792,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250611.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250611.csv</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -25972,7 +25864,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250612.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250612.csv</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -26044,7 +25936,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250613.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250613.csv</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -26116,7 +26008,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250614.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250614.csv</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -26188,7 +26080,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250615.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250615.csv</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -26260,7 +26152,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250616.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250616.csv</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -26332,7 +26224,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250617.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250617.csv</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -26404,7 +26296,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250618.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250618.csv</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -26476,7 +26368,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250619.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250619.csv</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -26548,7 +26440,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250620.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250620.csv</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -26620,7 +26512,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250621.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250621.csv</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -26692,7 +26584,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250622.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250622.csv</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -26764,7 +26656,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250623.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250623.csv</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -26836,7 +26728,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250624.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250624.csv</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -26908,7 +26800,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250625.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250625.csv</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -26980,7 +26872,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250626.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250626.csv</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -27052,7 +26944,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250627.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250627.csv</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -27124,7 +27016,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250628.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250628.csv</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -27196,7 +27088,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250629.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250629.csv</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -27268,7 +27160,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250630.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.06/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250630.csv</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -27340,7 +27232,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250701.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250701.csv</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -27412,7 +27304,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250702.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250702.csv</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -27484,7 +27376,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250703.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250703.csv</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -27556,7 +27448,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250704.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250704.csv</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -27628,7 +27520,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250705.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250705.csv</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -27700,7 +27592,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250706.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250706.csv</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -27772,7 +27664,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250707.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250707.csv</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -27844,7 +27736,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250708.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250708.csv</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -27916,7 +27808,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250709.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250709.csv</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -27988,7 +27880,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250710.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250710.csv</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -28060,7 +27952,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250711.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250711.csv</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -28132,7 +28024,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250712.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250712.csv</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -28204,7 +28096,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250713.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250713.csv</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -28276,7 +28168,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250714.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250714.csv</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -28348,7 +28240,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250715.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250715.csv</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -28420,7 +28312,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250716.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250716.csv</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -28492,7 +28384,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250717.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250717.csv</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -28564,7 +28456,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250718.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250718.csv</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -28636,7 +28528,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250719.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250719.csv</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -28708,7 +28600,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250720.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250720.csv</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -28780,7 +28672,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250721.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250721.csv</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -28852,7 +28744,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250722.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250722.csv</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -28924,7 +28816,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250723.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250723.csv</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -28996,7 +28888,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250724.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250724.csv</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -29068,7 +28960,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250725.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250725.csv</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -29140,7 +29032,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250726.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250726.csv</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -29212,7 +29104,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250727.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250727.csv</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -29284,7 +29176,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250728.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250728.csv</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -29356,7 +29248,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250729.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250729.csv</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -29428,7 +29320,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250730.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250730.csv</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -29500,7 +29392,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250731.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07/120_서울시 IOT 복합 센서(환경정보)_PUBDATA_20250731.csv</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -29572,7 +29464,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.07.28-08.03.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.07.28-08.03.csv</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -29644,7 +29536,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.08.04-08.10.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.08.04-08.10.csv</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -29716,7 +29608,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.08.11-08.17.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.08.11-08.17.csv</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -29788,7 +29680,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.08.18-08.24.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.08.18-08.24.csv</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -29860,7 +29752,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.08.25-08.31.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.08.25-08.31.csv</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -29932,7 +29824,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.09.01-09.07.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.09.01-09.07.csv</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -30004,7 +29896,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.09.08-09.14.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.09.08-09.14.csv</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -30076,7 +29968,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.09.15-09.21.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.09.15-09.21.csv</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -30148,7 +30040,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.09.22-09.28.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.09.22-09.28.csv</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -30220,7 +30112,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.09.29-10.05.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.09.29-10.05.csv</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -30292,7 +30184,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.10.06-10.12.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.10.06-10.12.csv</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -30364,7 +30256,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.10.13-10.19.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.10.13-10.19.csv</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -30436,7 +30328,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.10.20-10.26.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.10.20-10.26.csv</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -30508,7 +30400,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.10.27-11.02.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.10.27-11.02.csv</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -30580,7 +30472,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.11.03-11.09.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.11.03-11.09.csv</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -30652,7 +30544,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.11.10-11.16.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.11.10-11.16.csv</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -30724,7 +30616,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.11.17-11.23.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.11.17-11.23.csv</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -30796,7 +30688,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.11.24-11.30.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.11.24-11.30.csv</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -30868,7 +30760,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.12.01-12.07.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.12.01-12.07.csv</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -30940,7 +30832,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.12.08-12.14.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.12.08-12.14.csv</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -31012,7 +30904,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.12.15-12.21.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.12.15-12.21.csv</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -31084,7 +30976,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.12.22-12.28.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.12.22-12.28.csv</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -31156,7 +31048,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>S-DoT_2025/S-DoT_NATURE_2025.12.29-01.04.csv</t>
+          <t>S-DoT/S-DoT_2025/S-DoT_NATURE_2025.12.29-01.04.csv</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -31228,7 +31120,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.01.05-01.11.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.01.05-01.11.csv</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -31300,7 +31192,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.01.12-01.18.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.01.12-01.18.csv</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -31372,7 +31264,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.01.19-01.25.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.01.19-01.25.csv</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -31444,7 +31336,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.01.26-02.01.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.01.26-02.01.csv</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -31516,7 +31408,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.02.02-02.08.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.02.02-02.08.csv</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -31588,7 +31480,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.02.09-02.15.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.02.09-02.15.csv</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -31660,7 +31552,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.02.16-02.22.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.02.16-02.22.csv</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -31732,7 +31624,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.02.23-03.01.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.02.23-03.01.csv</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -31804,7 +31696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.03.02-03.08.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.03.02-03.08.csv</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -31876,7 +31768,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.03.09-03.15.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.03.09-03.15.csv</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -31948,7 +31840,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.03.16-03.22.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.03.16-03.22.csv</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -32020,7 +31912,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.03.23-03.29.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.03.23-03.29.csv</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -32092,7 +31984,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.03.30-04.05.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.03.30-04.05.csv</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -32164,7 +32056,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.04.06-04.12.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.04.06-04.12.csv</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -32236,7 +32128,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.04.13-04.19.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.04.13-04.19.csv</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -32308,7 +32200,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.04.20-04.26.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.04.20-04.26.csv</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -32380,7 +32272,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.04.27-05.03.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.04.27-05.03.csv</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -32452,7 +32344,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.05.04-05.10.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.05.04-05.10.csv</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -32524,7 +32416,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.05.11-05.17.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.05.11-05.17.csv</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -32596,7 +32488,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.05.18-05.24.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.05.18-05.24.csv</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -32668,7 +32560,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.05.25-05.31.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.05.25-05.31.csv</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -32740,7 +32632,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.06.01-06.07.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.06.01-06.07.csv</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -32812,7 +32704,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.06.08-06.14.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.06.08-06.14.csv</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -32884,7 +32776,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.06.15-06.21.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.06.15-06.21.csv</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -32956,7 +32848,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.06.22-06.28.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.06.22-06.28.csv</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -33028,7 +32920,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.06.29-07.05.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.06.29-07.05.csv</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -33100,7 +32992,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.07.06-07.12.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.07.06-07.12.csv</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -33172,7 +33064,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.07.13-07.19.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.07.13-07.19.csv</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -33244,7 +33136,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.07.20-07.26.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.07.20-07.26.csv</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -33316,7 +33208,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.07.27-08.02.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.07.27-08.02.csv</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -33388,7 +33280,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.08.03-08.09.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.08.03-08.09.csv</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -33460,7 +33352,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.08.10-08.16.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.08.10-08.16.csv</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -33532,7 +33424,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.08.17-08.23.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.08.17-08.23.csv</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -33604,7 +33496,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>S-DoT_2026/S-DoT_NATURE_2026.08.24-08.30.csv</t>
+          <t>S-DoT/S-DoT_2026/S-DoT_NATURE_2026.08.24-08.30.csv</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -33682,1472 +33574,1472 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>master_column</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>dtype</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>v2020_2022_corrupted</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>v2020_2022_recovered</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>v2023_onward</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>measure_time</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>datetime64[ns]</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr"/>
-      <c r="D2" s="0" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>전송시간</t>
         </is>
       </c>
-      <c r="E2" s="0" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>전송시간</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>측정시간</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>sensor_id</t>
         </is>
       </c>
-      <c r="B3" s="0" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="C3" s="0" t="inlineStr"/>
-      <c r="D3" s="0" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t>시리얼</t>
         </is>
       </c>
-      <c r="E3" s="0" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>시리얼</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>시리얼</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>temp_max</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr"/>
-      <c r="D4" s="0" t="inlineStr"/>
-      <c r="E4" s="0" t="inlineStr"/>
-      <c r="F4" s="0" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>온도 최대(℃)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>temp_avg</t>
         </is>
       </c>
-      <c r="B5" s="0" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr"/>
-      <c r="D5" s="0" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t>기온(℃), 기온 (℃)</t>
         </is>
       </c>
-      <c r="E5" s="0" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>기온(℃)</t>
         </is>
       </c>
-      <c r="F5" s="0" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>온도 평균(℃), 기온 (℃)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>temp_min</t>
         </is>
       </c>
-      <c r="B6" s="0" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C6" s="0" t="inlineStr"/>
-      <c r="D6" s="0" t="inlineStr"/>
-      <c r="E6" s="0" t="inlineStr"/>
-      <c r="F6" s="0" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>온도 최소(℃)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>humi_max</t>
         </is>
       </c>
-      <c r="B7" s="0" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr"/>
-      <c r="D7" s="0" t="inlineStr"/>
-      <c r="E7" s="0" t="inlineStr"/>
-      <c r="F7" s="0" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>습도 최대(%)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>humi_avg</t>
         </is>
       </c>
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr"/>
-      <c r="D8" s="0" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>상대습도(%), 상대습도 (%)</t>
         </is>
       </c>
-      <c r="E8" s="0" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>상대습도( %)</t>
         </is>
       </c>
-      <c r="F8" s="0" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>상대습도 (%), 습도 평균(%)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>humi_min</t>
         </is>
       </c>
-      <c r="B9" s="0" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C9" s="0" t="inlineStr"/>
-      <c r="D9" s="0" t="inlineStr"/>
-      <c r="E9" s="0" t="inlineStr"/>
-      <c r="F9" s="0" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
         <is>
           <t>습도 최소(%)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>wind_spd_max</t>
         </is>
       </c>
-      <c r="B10" s="0" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr"/>
-      <c r="D10" s="0" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t>돌풍 풍속(m/s), 돌풍 풍속 (m/s)</t>
         </is>
       </c>
-      <c r="E10" s="0" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>돌풍 풍속(m/s)</t>
         </is>
       </c>
-      <c r="F10" s="0" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>풍속 최대(m/s), 돌풍 풍속 (m/s)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>wind_spd_avg</t>
         </is>
       </c>
-      <c r="B11" s="0" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C11" s="0" t="inlineStr"/>
-      <c r="D11" s="0" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>풍속(m/s), 풍속 (m/s)</t>
         </is>
       </c>
-      <c r="E11" s="0" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>풍속(m/s)</t>
         </is>
       </c>
-      <c r="F11" s="0" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>풍속 평균(m/s), 풍속 (m/s)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>wind_spd_min</t>
         </is>
       </c>
-      <c r="B12" s="0" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C12" s="0" t="inlineStr"/>
-      <c r="D12" s="0" t="inlineStr"/>
-      <c r="E12" s="0" t="inlineStr"/>
-      <c r="F12" s="0" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
         <is>
           <t>풍속 최소(m/s)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>wind_dir_max</t>
         </is>
       </c>
-      <c r="B13" s="0" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C13" s="0" t="inlineStr"/>
-      <c r="D13" s="0" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>돌풍 풍향(°), 돌풍 풍향 (°)</t>
         </is>
       </c>
-      <c r="E13" s="0" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>돌풍 풍향(°)</t>
         </is>
       </c>
-      <c r="F13" s="0" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>풍향 최대(m/s), 돌풍 풍향 (°)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>wind_dir_avg</t>
         </is>
       </c>
-      <c r="B14" s="0" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C14" s="0" t="inlineStr"/>
-      <c r="D14" s="0" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>풍향 (°), 풍향(°)</t>
         </is>
       </c>
-      <c r="E14" s="0" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>풍향(°)</t>
         </is>
       </c>
-      <c r="F14" s="0" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>풍향 평균(m/s), 풍향 (°)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>wind_dir_min</t>
         </is>
       </c>
-      <c r="B15" s="0" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C15" s="0" t="inlineStr"/>
-      <c r="D15" s="0" t="inlineStr"/>
-      <c r="E15" s="0" t="inlineStr"/>
-      <c r="F15" s="0" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
         <is>
           <t>풍향 최소(m/s)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>illu_max</t>
         </is>
       </c>
-      <c r="B16" s="0" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C16" s="0" t="inlineStr"/>
-      <c r="D16" s="0" t="inlineStr"/>
-      <c r="E16" s="0" t="inlineStr"/>
-      <c r="F16" s="0" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
         <is>
           <t>조도 최대(lux)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>illu_avg</t>
         </is>
       </c>
-      <c r="B17" s="0" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C17" s="0" t="inlineStr"/>
-      <c r="D17" s="0" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>조도(lux), 조도 (lux)</t>
         </is>
       </c>
-      <c r="E17" s="0" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>조도(lux)</t>
         </is>
       </c>
-      <c r="F17" s="0" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>조도 평균(lux), 조도 (lux)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="0" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>illu_min</t>
         </is>
       </c>
-      <c r="B18" s="0" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C18" s="0" t="inlineStr"/>
-      <c r="D18" s="0" t="inlineStr"/>
-      <c r="E18" s="0" t="inlineStr"/>
-      <c r="F18" s="0" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
         <is>
           <t>조도 최소(lux)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="0" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>uv_max</t>
         </is>
       </c>
-      <c r="B19" s="0" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C19" s="0" t="inlineStr"/>
-      <c r="D19" s="0" t="inlineStr"/>
-      <c r="E19" s="0" t="inlineStr"/>
-      <c r="F19" s="0" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
         <is>
           <t>자외선 최대(UV).1, 자외선 최대(UV)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="0" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>uv_avg</t>
         </is>
       </c>
-      <c r="B20" s="0" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C20" s="0" t="inlineStr"/>
-      <c r="D20" s="0" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t>자외선 (UVI), 자외선(UVI)</t>
         </is>
       </c>
-      <c r="E20" s="0" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>자외선(UVI)</t>
         </is>
       </c>
-      <c r="F20" s="0" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>자외선 (UVI), 자외선 평균(UV)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="0" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>uv_min</t>
         </is>
       </c>
-      <c r="B21" s="0" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C21" s="0" t="inlineStr"/>
-      <c r="D21" s="0" t="inlineStr"/>
-      <c r="E21" s="0" t="inlineStr"/>
-      <c r="F21" s="0" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
         <is>
           <t>자외선 최소(UV)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="0" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>noise_max</t>
         </is>
       </c>
-      <c r="B22" s="0" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C22" s="0" t="inlineStr"/>
-      <c r="D22" s="0" t="inlineStr"/>
-      <c r="E22" s="0" t="inlineStr"/>
-      <c r="F22" s="0" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
         <is>
           <t>소음 최대(dB)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="0" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>noise_avg</t>
         </is>
       </c>
-      <c r="B23" s="0" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C23" s="0" t="inlineStr"/>
-      <c r="D23" s="0" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>소음 (㏈), 소음(dB)</t>
         </is>
       </c>
-      <c r="E23" s="0" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>소음(dB)</t>
         </is>
       </c>
-      <c r="F23" s="0" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>소음 평균(dB), 소음 (dB)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="0" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>noise_min</t>
         </is>
       </c>
-      <c r="B24" s="0" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C24" s="0" t="inlineStr"/>
-      <c r="D24" s="0" t="inlineStr"/>
-      <c r="E24" s="0" t="inlineStr"/>
-      <c r="F24" s="0" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
         <is>
           <t>소음 최소(dB)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="0" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>vibe_x_max_g</t>
         </is>
       </c>
-      <c r="B25" s="0" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C25" s="0" t="inlineStr"/>
-      <c r="D25" s="0" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t>진동_x 최대(g)), 진동(x) 최대 (g)</t>
         </is>
       </c>
-      <c r="E25" s="0" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>진동_x 최대(g)</t>
         </is>
       </c>
-      <c r="F25" s="0" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>진동(x) 최대 (g)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="0" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>vibe_x_avg_g</t>
         </is>
       </c>
-      <c r="B26" s="0" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C26" s="0" t="inlineStr"/>
-      <c r="D26" s="0" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t>진동(x) (g), 진동_(x)(g)</t>
         </is>
       </c>
-      <c r="E26" s="0" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>진동_x(g)</t>
         </is>
       </c>
-      <c r="F26" s="0" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>진동(x) (g)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="0" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>vibe_x_min_g</t>
         </is>
       </c>
-      <c r="B27" s="0" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C27" s="0" t="inlineStr"/>
-      <c r="D27" s="0" t="inlineStr"/>
-      <c r="E27" s="0" t="inlineStr"/>
-      <c r="F27" s="0" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="0" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>vibe_y_max_g</t>
         </is>
       </c>
-      <c r="B28" s="0" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C28" s="0" t="inlineStr"/>
-      <c r="D28" s="0" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t>진동_y 최대(g), 진동(y) 최대 (g)</t>
         </is>
       </c>
-      <c r="E28" s="0" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>진동_y 최대(g)</t>
         </is>
       </c>
-      <c r="F28" s="0" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>진동(y) 최대 (g)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="0" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>vibe_y_avg_g</t>
         </is>
       </c>
-      <c r="B29" s="0" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C29" s="0" t="inlineStr"/>
-      <c r="D29" s="0" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>진동_(y)(g), 진동(y) (g)</t>
         </is>
       </c>
-      <c r="E29" s="0" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>진동_y(g)</t>
         </is>
       </c>
-      <c r="F29" s="0" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>진동(y) (g)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="0" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>vibe_y_min_g</t>
         </is>
       </c>
-      <c r="B30" s="0" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C30" s="0" t="inlineStr"/>
-      <c r="D30" s="0" t="inlineStr"/>
-      <c r="E30" s="0" t="inlineStr"/>
-      <c r="F30" s="0" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="0" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>vibe_z_max_g</t>
         </is>
       </c>
-      <c r="B31" s="0" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C31" s="0" t="inlineStr"/>
-      <c r="D31" s="0" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>진동_z 최대(g), 진동(z) 최대 (g)</t>
         </is>
       </c>
-      <c r="E31" s="0" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>진동_z 최대(g)</t>
         </is>
       </c>
-      <c r="F31" s="0" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>진동(z) 최대 (g)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="0" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>vibe_z_avg_g</t>
         </is>
       </c>
-      <c r="B32" s="0" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C32" s="0" t="inlineStr"/>
-      <c r="D32" s="0" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>진동_(z)(g), 진동(z) (g)</t>
         </is>
       </c>
-      <c r="E32" s="0" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>진동_z(g)</t>
         </is>
       </c>
-      <c r="F32" s="0" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>진동(z) (g)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="0" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>vibe_z_min_g</t>
         </is>
       </c>
-      <c r="B33" s="0" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C33" s="0" t="inlineStr"/>
-      <c r="D33" s="0" t="inlineStr"/>
-      <c r="E33" s="0" t="inlineStr"/>
-      <c r="F33" s="0" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="0" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>vibe_x_max_mms</t>
         </is>
       </c>
-      <c r="B34" s="0" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C34" s="0" t="inlineStr"/>
-      <c r="D34" s="0" t="inlineStr"/>
-      <c r="E34" s="0" t="inlineStr"/>
-      <c r="F34" s="0" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
         <is>
           <t>진동(x) 최대(mm/s)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="0" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>vibe_x_avg_mms</t>
         </is>
       </c>
-      <c r="B35" s="0" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C35" s="0" t="inlineStr"/>
-      <c r="D35" s="0" t="inlineStr"/>
-      <c r="E35" s="0" t="inlineStr"/>
-      <c r="F35" s="0" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
         <is>
           <t>진동(x) 평균(mm/s)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="0" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>vibe_x_min_mms</t>
         </is>
       </c>
-      <c r="B36" s="0" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C36" s="0" t="inlineStr"/>
-      <c r="D36" s="0" t="inlineStr"/>
-      <c r="E36" s="0" t="inlineStr"/>
-      <c r="F36" s="0" t="inlineStr">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
         <is>
           <t>진동(x) 최소(mm/s)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="0" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>vibe_y_max_mms</t>
         </is>
       </c>
-      <c r="B37" s="0" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C37" s="0" t="inlineStr"/>
-      <c r="D37" s="0" t="inlineStr"/>
-      <c r="E37" s="0" t="inlineStr"/>
-      <c r="F37" s="0" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
         <is>
           <t>진동(y) 최대(mm/s)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="0" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>vibe_y_avg_mms</t>
         </is>
       </c>
-      <c r="B38" s="0" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C38" s="0" t="inlineStr"/>
-      <c r="D38" s="0" t="inlineStr"/>
-      <c r="E38" s="0" t="inlineStr"/>
-      <c r="F38" s="0" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
         <is>
           <t>진동(y) 평균(mm/s)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="0" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>vibe_y_min_mms</t>
         </is>
       </c>
-      <c r="B39" s="0" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C39" s="0" t="inlineStr"/>
-      <c r="D39" s="0" t="inlineStr"/>
-      <c r="E39" s="0" t="inlineStr"/>
-      <c r="F39" s="0" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
         <is>
           <t>진동(y) 최소(mm/s)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="0" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>vibe_z_max_mms</t>
         </is>
       </c>
-      <c r="B40" s="0" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C40" s="0" t="inlineStr"/>
-      <c r="D40" s="0" t="inlineStr"/>
-      <c r="E40" s="0" t="inlineStr"/>
-      <c r="F40" s="0" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
         <is>
           <t>진동(z) 최대(mm/s)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="0" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>vibe_z_avg_mms</t>
         </is>
       </c>
-      <c r="B41" s="0" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C41" s="0" t="inlineStr"/>
-      <c r="D41" s="0" t="inlineStr"/>
-      <c r="E41" s="0" t="inlineStr"/>
-      <c r="F41" s="0" t="inlineStr">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
         <is>
           <t>진동(z) 평균(mm/s)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="0" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>vibe_z_min_mms</t>
         </is>
       </c>
-      <c r="B42" s="0" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C42" s="0" t="inlineStr"/>
-      <c r="D42" s="0" t="inlineStr"/>
-      <c r="E42" s="0" t="inlineStr"/>
-      <c r="F42" s="0" t="inlineStr">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
         <is>
           <t>진동(z) 최소(mm/s)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="0" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>wbgt_max</t>
         </is>
       </c>
-      <c r="B43" s="0" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C43" s="0" t="inlineStr"/>
-      <c r="D43" s="0" t="inlineStr"/>
-      <c r="E43" s="0" t="inlineStr"/>
-      <c r="F43" s="0" t="inlineStr">
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
         <is>
           <t>흑구온도 최대(℃)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="0" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>wbgt_avg</t>
         </is>
       </c>
-      <c r="B44" s="0" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C44" s="0" t="inlineStr"/>
-      <c r="D44" s="0" t="inlineStr">
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
         <is>
           <t>흑구 온도(℃), 흑구 온도 (℃)</t>
         </is>
       </c>
-      <c r="E44" s="0" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>흑구 온도(℃), 흑구 운도(℃)</t>
         </is>
       </c>
-      <c r="F44" s="0" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>흑구온도 평균(℃), 흑구 온도 (℃)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="0" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>wbgt_min</t>
         </is>
       </c>
-      <c r="B45" s="0" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C45" s="0" t="inlineStr"/>
-      <c r="D45" s="0" t="inlineStr"/>
-      <c r="E45" s="0" t="inlineStr"/>
-      <c r="F45" s="0" t="inlineStr">
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
         <is>
           <t>흑구온도 최소(℃)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="0" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>no2_max</t>
         </is>
       </c>
-      <c r="B46" s="0" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C46" s="0" t="inlineStr"/>
-      <c r="D46" s="0" t="inlineStr"/>
-      <c r="E46" s="0" t="inlineStr"/>
-      <c r="F46" s="0" t="inlineStr">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
         <is>
           <t>이산화질소 최대(pPM), 이산화질소 최대(ppm)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="0" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>no2_avg</t>
         </is>
       </c>
-      <c r="B47" s="0" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C47" s="0" t="inlineStr"/>
-      <c r="D47" s="0" t="inlineStr">
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
         <is>
           <t>이산화질소</t>
         </is>
       </c>
-      <c r="E47" s="0" t="inlineStr"/>
-      <c r="F47" s="0" t="inlineStr">
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
         <is>
           <t>이산화질소 평균(ppm), 이산화질소 평균(pPM)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="0" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>no2_min</t>
         </is>
       </c>
-      <c r="B48" s="0" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C48" s="0" t="inlineStr"/>
-      <c r="D48" s="0" t="inlineStr"/>
-      <c r="E48" s="0" t="inlineStr"/>
-      <c r="F48" s="0" t="inlineStr">
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
         <is>
           <t>이산화질소 최소(pPM), 이산화질소 최소(ppm)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="0" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>co_max</t>
         </is>
       </c>
-      <c r="B49" s="0" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C49" s="0" t="inlineStr"/>
-      <c r="D49" s="0" t="inlineStr"/>
-      <c r="E49" s="0" t="inlineStr"/>
-      <c r="F49" s="0" t="inlineStr">
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
         <is>
           <t>일산화탄소 최대(pPM), 일산화탄소 최대(ppm)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="0" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>co_avg</t>
         </is>
       </c>
-      <c r="B50" s="0" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C50" s="0" t="inlineStr"/>
-      <c r="D50" s="0" t="inlineStr">
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
         <is>
           <t>일산화탄소</t>
         </is>
       </c>
-      <c r="E50" s="0" t="inlineStr"/>
-      <c r="F50" s="0" t="inlineStr">
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
         <is>
           <t>일산화탄소 평균(pPM), 일산화탄소 평균(ppm)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="0" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>co_min</t>
         </is>
       </c>
-      <c r="B51" s="0" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C51" s="0" t="inlineStr"/>
-      <c r="D51" s="0" t="inlineStr"/>
-      <c r="E51" s="0" t="inlineStr"/>
-      <c r="F51" s="0" t="inlineStr">
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
         <is>
           <t>일산화탄소 최소(pPM), 일산화탄소 최소(ppm)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="0" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>so2_max</t>
         </is>
       </c>
-      <c r="B52" s="0" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C52" s="0" t="inlineStr"/>
-      <c r="D52" s="0" t="inlineStr"/>
-      <c r="E52" s="0" t="inlineStr"/>
-      <c r="F52" s="0" t="inlineStr">
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
         <is>
           <t>이산화황 최대(pPM), 이산화황 최대(ppm)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="0" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>so2_avg</t>
         </is>
       </c>
-      <c r="B53" s="0" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C53" s="0" t="inlineStr"/>
-      <c r="D53" s="0" t="inlineStr">
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
         <is>
           <t>이산화황</t>
         </is>
       </c>
-      <c r="E53" s="0" t="inlineStr"/>
-      <c r="F53" s="0" t="inlineStr">
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
         <is>
           <t>이산화황 평균(ppm), 이산화황 평균(pPM)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="0" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>so2_min</t>
         </is>
       </c>
-      <c r="B54" s="0" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C54" s="0" t="inlineStr"/>
-      <c r="D54" s="0" t="inlineStr"/>
-      <c r="E54" s="0" t="inlineStr"/>
-      <c r="F54" s="0" t="inlineStr">
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
         <is>
           <t>이산화황 최소(ppm), 이산화황 최소(pPM)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="0" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>nh3_max</t>
         </is>
       </c>
-      <c r="B55" s="0" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C55" s="0" t="inlineStr"/>
-      <c r="D55" s="0" t="inlineStr"/>
-      <c r="E55" s="0" t="inlineStr"/>
-      <c r="F55" s="0" t="inlineStr">
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
         <is>
           <t>암모니아 최대(ppm), 암모니아 최대(pPM)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="0" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>nh3_avg</t>
         </is>
       </c>
-      <c r="B56" s="0" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C56" s="0" t="inlineStr"/>
-      <c r="D56" s="0" t="inlineStr">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
         <is>
           <t>암모니아</t>
         </is>
       </c>
-      <c r="E56" s="0" t="inlineStr"/>
-      <c r="F56" s="0" t="inlineStr">
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
         <is>
           <t>암모니아 평균(ppm), 암모니아 평균(pPM)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="0" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>nh3_min</t>
         </is>
       </c>
-      <c r="B57" s="0" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C57" s="0" t="inlineStr"/>
-      <c r="D57" s="0" t="inlineStr"/>
-      <c r="E57" s="0" t="inlineStr"/>
-      <c r="F57" s="0" t="inlineStr">
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
         <is>
           <t>암모니아 최소(ppm), 암모니아 최소(pPM)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="0" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>h2s_max</t>
         </is>
       </c>
-      <c r="B58" s="0" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C58" s="0" t="inlineStr"/>
-      <c r="D58" s="0" t="inlineStr"/>
-      <c r="E58" s="0" t="inlineStr"/>
-      <c r="F58" s="0" t="inlineStr">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
         <is>
           <t>황화수소 최대(pPM), 황화수소 최대(ppm)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="0" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>h2s_avg</t>
         </is>
       </c>
-      <c r="B59" s="0" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C59" s="0" t="inlineStr"/>
-      <c r="D59" s="0" t="inlineStr">
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
         <is>
           <t>황화수소</t>
         </is>
       </c>
-      <c r="E59" s="0" t="inlineStr"/>
-      <c r="F59" s="0" t="inlineStr">
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
         <is>
           <t>황화수소 평균(pPM), 황화수소 평균(ppm)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="0" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>h2s_min</t>
         </is>
       </c>
-      <c r="B60" s="0" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C60" s="0" t="inlineStr"/>
-      <c r="D60" s="0" t="inlineStr"/>
-      <c r="E60" s="0" t="inlineStr"/>
-      <c r="F60" s="0" t="inlineStr">
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
         <is>
           <t>황화수소 최소(pPM), 황화수소 최소(ppm)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="0" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>o3_max</t>
         </is>
       </c>
-      <c r="B61" s="0" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C61" s="0" t="inlineStr"/>
-      <c r="D61" s="0" t="inlineStr"/>
-      <c r="E61" s="0" t="inlineStr"/>
-      <c r="F61" s="0" t="inlineStr">
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
         <is>
           <t>오존 최대(ppm), 오존 최대(pPM)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="0" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>o3_avg</t>
         </is>
       </c>
-      <c r="B62" s="0" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C62" s="0" t="inlineStr"/>
-      <c r="D62" s="0" t="inlineStr">
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
         <is>
           <t>오존</t>
         </is>
       </c>
-      <c r="E62" s="0" t="inlineStr"/>
-      <c r="F62" s="0" t="inlineStr">
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
         <is>
           <t>오존 평균(ppm), 오존 평균(pPM)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="0" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>o3_min</t>
         </is>
       </c>
-      <c r="B63" s="0" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C63" s="0" t="inlineStr"/>
-      <c r="D63" s="0" t="inlineStr"/>
-      <c r="E63" s="0" t="inlineStr"/>
-      <c r="F63" s="0" t="inlineStr">
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
         <is>
           <t>오존 최소(pPM), 오존 최소(ppm)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="0" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>pm10</t>
         </is>
       </c>
-      <c r="B64" s="0" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C64" s="0" t="inlineStr"/>
-      <c r="D64" s="0" t="inlineStr"/>
-      <c r="E64" s="0" t="inlineStr">
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
         <is>
           <t>미세먼지 보정(㎍/㎥)</t>
         </is>
       </c>
-      <c r="F64" s="0" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="0" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>pm25</t>
         </is>
       </c>
-      <c r="B65" s="0" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>float64</t>
         </is>
       </c>
-      <c r="C65" s="0" t="inlineStr"/>
-      <c r="D65" s="0" t="inlineStr"/>
-      <c r="E65" s="0" t="inlineStr">
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
         <is>
           <t>초미세먼지 보정(㎍/㎥)</t>
         </is>
       </c>
-      <c r="F65" s="0" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
